--- a/docs/Final_Project_UI_Ehate_Statusu.xlsx
+++ b/docs/Final_Project_UI_Ehate_Statusu.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="81">
   <si>
     <t xml:space="preserve">Modul</t>
   </si>
@@ -86,118 +86,124 @@
     <t xml:space="preserve">Ana səhifə</t>
   </si>
   <si>
+    <t xml:space="preserve">Orta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Konsol xətaları və tətbiq mağazası linkləri əl ilə</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valyuta konvertoru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUG-014, OBS-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filiallar və ATM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tab keçidləri və xəritə konteyneri yoxlanır; OBS-003 rədd edildi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marker və axtarış (Google Maps) əl ilə yoxlanır</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axtarış</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUG-015, 016, OBS-004, 005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Responsiv və mobil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamburger menyu, üfüqi sürüşmə, kalkulyator (500px); mobil menyu linkləri BUG-013-ə daxildir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">320px və 768px əl ilə</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kartlar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OBS-007, 008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kart detalları və sıralama manual qalır</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kreditlər</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUG-023, OBS-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faiz/şərt mətninin kalkulyatorla uyğunluğu yoxlanmayıb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Əmanətlər</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUG-018, 019, 022, OBS-013, 014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum məbləğ və USD/EUR seçimi əl ilə yoxlanmalıdır</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pul köçürmələri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real köçürmə testi tələb olunmur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Onlayn xidmətlər</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OBS-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">İnternet bankçılıq girişinə toxunulmur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digər xidmətlər</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUG-017 (başlıqlar); FAQ akkordeonu avtomatlaşdırılıb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qalan alt səhifələr və PDF-lər əl ilə</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kampaniyalar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vaxtı bitmiş kampaniya yoxlanmayıb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biznes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUG-017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biznes kreditləri bölməsi əl ilə</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank haqqında</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OBS-011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rəhbərlik və hesabatlar əl ilə</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xəbərlər</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Təhlükəsizlik</t>
+  </si>
+  <si>
     <t xml:space="preserve">Əl ilə baxılıb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avtomatlaşdırma lazım olarsa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valyuta konvertoru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUG-014, OBS-002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filiallar və ATM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tab keçidləri və xəritə konteyneri yoxlanır; OBS-003 rədd edildi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marker və axtarış (Google Maps) əl ilə yoxlanır</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axtarış</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUG-015, 016, OBS-004, 005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Responsiv və mobil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamburger menyu, üfüqi sürüşmə, kalkulyator (500px); mobil menyu linkləri BUG-013-ə daxildir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">320px və 768px əl ilə</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kartlar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OBS-007, 008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kart detalları və sıralama manual qalır</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kreditlər</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUG-023, OBS-007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Faiz/şərt mətninin kalkulyatorla uyğunluğu yoxlanmayıb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Əmanətlər</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUG-018, 019, 022, OBS-013, 014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minimum məbləğ və USD/EUR seçimi əl ilə yoxlanmalıdır</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pul köçürmələri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real köçürmə testi tələb olunmur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Onlayn xidmətlər</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OBS-006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Digər xidmətlər</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUG-017 (başlıqlar); 17 alt səhifə və PDF-lər yoxlanıb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FAQ akkordeonu yoxlanmayıb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kampaniyalar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vaxtı bitmiş kampaniya yoxlanmayıb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Biznes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUG-017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Biznes kreditləri bölməsi yoxlanmayıb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bank haqqında</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OBS-011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xəbərlər</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Təhlükəsizlik</t>
   </si>
   <si>
     <t xml:space="preserve">Aşağı</t>
@@ -798,24 +804,24 @@
         <v>19</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="D6" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>7</v>
@@ -827,7 +833,7 @@
         <v>2</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>10</v>
@@ -835,7 +841,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>7</v>
@@ -847,15 +853,15 @@
         <v>4</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>7</v>
@@ -867,7 +873,7 @@
         <v>3</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>10</v>
@@ -875,7 +881,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>7</v>
@@ -887,110 +893,110 @@
         <v>4</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="E12" s="3" t="s">
+      <c r="F12" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>8</v>
       </c>
       <c r="E13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="D14" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3" t="s">
+      <c r="F15" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -998,13 +1004,13 @@
         <v>46</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="D16" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>47</v>
@@ -1018,13 +1024,13 @@
         <v>49</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="D17" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>10</v>
@@ -1038,13 +1044,13 @@
         <v>51</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="D18" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>52</v>
@@ -1058,33 +1064,33 @@
         <v>54</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="D19" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="D20" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>10</v>
@@ -1095,102 +1101,102 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1226,15 +1232,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B2" s="5" t="n">
         <f aca="false">COUNTA('Əhatə statusu'!A2:A25)</f>
@@ -1247,21 +1253,21 @@
       </c>
       <c r="B3" s="5" t="n">
         <f aca="false">COUNTIF('Əhatə statusu'!B2:B25,"Avtomatlaşdırılıb")</f>
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="B4" s="5" t="n">
         <f aca="false">COUNTIF('Əhatə statusu'!B2:B25,"Əl ilə baxılıb")</f>
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B5" s="5" t="n">
         <f aca="false">COUNTIF('Əhatə statusu'!B2:B25,"İcra olunmayıb")</f>
@@ -1274,21 +1280,21 @@
       </c>
       <c r="B6" s="5" t="n">
         <f aca="false">SUM('Əhatə statusu'!D2:D25)</f>
-        <v>65</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B7" s="6" t="n">
         <f aca="false">B3/B2</f>
-        <v>0.5</v>
+        <v>0.833333333333333</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B8" s="5" t="n">
         <f aca="false">COUNTIFS('Əhatə statusu'!B2:B25,"İcra olunmayıb",'Əhatə statusu'!C2:C25,"Yüksək")</f>

--- a/docs/Final_Project_UI_Ehate_Statusu.xlsx
+++ b/docs/Final_Project_UI_Ehate_Statusu.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="83">
   <si>
     <t xml:space="preserve">Modul</t>
   </si>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">Yüksək</t>
   </si>
   <si>
-    <t xml:space="preserve">BUG-008, 009, 010</t>
+    <t xml:space="preserve">BUG-008, 009, 010; OBS-016</t>
   </si>
   <si>
     <t xml:space="preserve">-</t>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">Kredit kalkulyatoru</t>
   </si>
   <si>
-    <t xml:space="preserve">BUG-001, 002, 003, 005, 007 (004, 006 hələ avtomatlaşdırılmayıb)</t>
+    <t xml:space="preserve">BUG-001, 002, 003, 005, 007 (004, 006 hələ avtomatlaşdırılmayıb); BUG-024</t>
   </si>
   <si>
     <t xml:space="preserve">BUG-004, 006 üçün ssenari</t>
@@ -89,7 +89,10 @@
     <t xml:space="preserve">Orta</t>
   </si>
   <si>
-    <t xml:space="preserve">Konsol xətaları və tətbiq mağazası linkləri əl ilə</t>
+    <t xml:space="preserve">BUG-025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mağaza linkləri və şəkillər yoxlanıldı; karusel əl ilə qalır</t>
   </si>
   <si>
     <t xml:space="preserve">Valyuta konvertoru</t>
@@ -104,7 +107,7 @@
     <t xml:space="preserve">Tab keçidləri və xəritə konteyneri yoxlanır; OBS-003 rədd edildi</t>
   </si>
   <si>
-    <t xml:space="preserve">Marker və axtarış (Google Maps) əl ilə yoxlanır</t>
+    <t xml:space="preserve">Marker və tablar yoxlanıldı; axtarış sahəsi yoxdur</t>
   </si>
   <si>
     <t xml:space="preserve">Axtarış</t>
@@ -119,7 +122,7 @@
     <t xml:space="preserve">Hamburger menyu, üfüqi sürüşmə, kalkulyator (500px); mobil menyu linkləri BUG-013-ə daxildir</t>
   </si>
   <si>
-    <t xml:space="preserve">320px və 768px əl ilə</t>
+    <t xml:space="preserve">320/768/1024/1920 və landşaft əl ilə yoxlanıldı</t>
   </si>
   <si>
     <t xml:space="preserve">Kartlar</t>
@@ -137,16 +140,16 @@
     <t xml:space="preserve">BUG-023, OBS-007</t>
   </si>
   <si>
-    <t xml:space="preserve">Faiz/şərt mətninin kalkulyatorla uyğunluğu yoxlanmayıb</t>
+    <t xml:space="preserve">Faiz və şərtlər kalkulyatorla uyğundur</t>
   </si>
   <si>
     <t xml:space="preserve">Əmanətlər</t>
   </si>
   <si>
-    <t xml:space="preserve">BUG-018, 019, 022, OBS-013, 014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minimum məbləğ və USD/EUR seçimi əl ilə yoxlanmalıdır</t>
+    <t xml:space="preserve">BUG-018, 019, 022, OBS-013, 014; BUG-026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USD seçimi yoxlanıldı; minimum məbləğ nəticəsi BUG-026</t>
   </si>
   <si>
     <t xml:space="preserve">Pul köçürmələri</t>
@@ -176,7 +179,10 @@
     <t xml:space="preserve">Kampaniyalar</t>
   </si>
   <si>
-    <t xml:space="preserve">Vaxtı bitmiş kampaniya yoxlanmayıb</t>
+    <t xml:space="preserve">OBS-015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detal səhifəsi yoxlanıldı; bitmiş kampaniya siyahıdadır</t>
   </si>
   <si>
     <t xml:space="preserve">Biznes</t>
@@ -185,7 +191,7 @@
     <t xml:space="preserve">BUG-017</t>
   </si>
   <si>
-    <t xml:space="preserve">Biznes kreditləri bölməsi əl ilə</t>
+    <t xml:space="preserve">Biznes bölməsi yoxlanıldı</t>
   </si>
   <si>
     <t xml:space="preserve">Bank haqqında</t>
@@ -212,7 +218,7 @@
     <t xml:space="preserve">OBS-009, OBS-010</t>
   </si>
   <si>
-    <t xml:space="preserve">HTTP→HTTPS və kuki bayraqları yoxlanmayıb</t>
+    <t xml:space="preserve">HTTPS avtomatik yoxlanılıb; kuki bayraqları icra olunmayıb</t>
   </si>
   <si>
     <t xml:space="preserve">Xarici linklər</t>
@@ -230,7 +236,7 @@
     <t xml:space="preserve">BUG-020</t>
   </si>
   <si>
-    <t xml:space="preserve">Kontrast və klaviatura fokusu yoxlanmayıb</t>
+    <t xml:space="preserve">Widget yoxlanıldı; kontrast və fokus icra olunmayıb</t>
   </si>
   <si>
     <t xml:space="preserve">Performans və SEO</t>
@@ -813,15 +819,15 @@
         <v>6</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>7</v>
@@ -833,7 +839,7 @@
         <v>2</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>10</v>
@@ -841,7 +847,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>7</v>
@@ -853,15 +859,15 @@
         <v>4</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>7</v>
@@ -873,7 +879,7 @@
         <v>3</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>10</v>
@@ -881,7 +887,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>7</v>
@@ -893,15 +899,15 @@
         <v>4</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>7</v>
@@ -913,15 +919,15 @@
         <v>4</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>7</v>
@@ -933,15 +939,15 @@
         <v>7</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>7</v>
@@ -953,15 +959,15 @@
         <v>8</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>7</v>
@@ -976,12 +982,12 @@
         <v>10</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>7</v>
@@ -993,15 +999,15 @@
         <v>2</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>7</v>
@@ -1013,15 +1019,15 @@
         <v>10</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>7</v>
@@ -1033,15 +1039,15 @@
         <v>2</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>7</v>
@@ -1053,15 +1059,15 @@
         <v>1</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>7</v>
@@ -1073,15 +1079,15 @@
         <v>1</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>7</v>
@@ -1101,102 +1107,102 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1232,15 +1238,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B2" s="5" t="n">
         <f aca="false">COUNTA('Əhatə statusu'!A2:A25)</f>
@@ -1258,7 +1264,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B4" s="5" t="n">
         <f aca="false">COUNTIF('Əhatə statusu'!B2:B25,"Əl ilə baxılıb")</f>
@@ -1267,7 +1273,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B5" s="5" t="n">
         <f aca="false">COUNTIF('Əhatə statusu'!B2:B25,"İcra olunmayıb")</f>
@@ -1285,7 +1291,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B7" s="6" t="n">
         <f aca="false">B3/B2</f>
@@ -1294,7 +1300,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B8" s="5" t="n">
         <f aca="false">COUNTIFS('Əhatə statusu'!B2:B25,"İcra olunmayıb",'Əhatə statusu'!C2:C25,"Yüksək")</f>

--- a/docs/Final_Project_UI_Ehate_Statusu.xlsx
+++ b/docs/Final_Project_UI_Ehate_Statusu.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="79">
   <si>
     <t xml:space="preserve">Modul</t>
   </si>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">Yüksək</t>
   </si>
   <si>
-    <t xml:space="preserve">BUG-008, 009, 010; OBS-016</t>
+    <t xml:space="preserve">BUG-008, 009, 010, 032</t>
   </si>
   <si>
     <t xml:space="preserve">-</t>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">Kredit kalkulyatoru</t>
   </si>
   <si>
-    <t xml:space="preserve">BUG-001, 002, 003, 005, 007 (004, 006 hələ avtomatlaşdırılmayıb); BUG-024</t>
+    <t xml:space="preserve">BUG-001, 002, 003, 005, 007, 024 (004, 006 hələ avtomatlaşdırılmayıb)</t>
   </si>
   <si>
     <t xml:space="preserve">BUG-004, 006 üçün ssenari</t>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">Naviqasiya və menyu</t>
   </si>
   <si>
-    <t xml:space="preserve">BUG-011, 013 (BUG-012 rədd edildi)</t>
+    <t xml:space="preserve">BUG-011, 013</t>
   </si>
   <si>
     <t xml:space="preserve">BUG-011 real Chrome-da təsdiqləndi</t>
@@ -80,9 +80,6 @@
     <t xml:space="preserve">Valyuta məzənnəsi (cədvəl)</t>
   </si>
   <si>
-    <t xml:space="preserve">OBS-001</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ana səhifə</t>
   </si>
   <si>
@@ -98,13 +95,13 @@
     <t xml:space="preserve">Valyuta konvertoru</t>
   </si>
   <si>
-    <t xml:space="preserve">BUG-014, OBS-002</t>
+    <t xml:space="preserve">BUG-014</t>
   </si>
   <si>
     <t xml:space="preserve">Filiallar və ATM</t>
   </si>
   <si>
-    <t xml:space="preserve">Tab keçidləri və xəritə konteyneri yoxlanır; OBS-003 rədd edildi</t>
+    <t xml:space="preserve">Tab keçidləri və xəritə konteyneri yoxlanır</t>
   </si>
   <si>
     <t xml:space="preserve">Marker və tablar yoxlanıldı; axtarış sahəsi yoxdur</t>
@@ -113,7 +110,7 @@
     <t xml:space="preserve">Axtarış</t>
   </si>
   <si>
-    <t xml:space="preserve">BUG-015, 016, OBS-004, 005</t>
+    <t xml:space="preserve">BUG-015, 016, 027, 028</t>
   </si>
   <si>
     <t xml:space="preserve">Responsiv və mobil</t>
@@ -128,7 +125,7 @@
     <t xml:space="preserve">Kartlar</t>
   </si>
   <si>
-    <t xml:space="preserve">OBS-007, 008</t>
+    <t xml:space="preserve">BUG-029</t>
   </si>
   <si>
     <t xml:space="preserve">Kart detalları və sıralama manual qalır</t>
@@ -137,7 +134,7 @@
     <t xml:space="preserve">Kreditlər</t>
   </si>
   <si>
-    <t xml:space="preserve">BUG-023, OBS-007</t>
+    <t xml:space="preserve">BUG-023</t>
   </si>
   <si>
     <t xml:space="preserve">Faiz və şərtlər kalkulyatorla uyğundur</t>
@@ -146,7 +143,7 @@
     <t xml:space="preserve">Əmanətlər</t>
   </si>
   <si>
-    <t xml:space="preserve">BUG-018, 019, 022, OBS-013, 014; BUG-026</t>
+    <t xml:space="preserve">BUG-018, 019, 022, 026</t>
   </si>
   <si>
     <t xml:space="preserve">USD seçimi yoxlanıldı; minimum məbləğ nəticəsi BUG-026</t>
@@ -161,9 +158,6 @@
     <t xml:space="preserve">Onlayn xidmətlər</t>
   </si>
   <si>
-    <t xml:space="preserve">OBS-006</t>
-  </si>
-  <si>
     <t xml:space="preserve">İnternet bankçılıq girişinə toxunulmur</t>
   </si>
   <si>
@@ -179,7 +173,7 @@
     <t xml:space="preserve">Kampaniyalar</t>
   </si>
   <si>
-    <t xml:space="preserve">OBS-015</t>
+    <t xml:space="preserve">BUG-031</t>
   </si>
   <si>
     <t xml:space="preserve">Detal səhifəsi yoxlanıldı; bitmiş kampaniya siyahıdadır</t>
@@ -197,7 +191,7 @@
     <t xml:space="preserve">Bank haqqında</t>
   </si>
   <si>
-    <t xml:space="preserve">OBS-011</t>
+    <t xml:space="preserve">BUG-030</t>
   </si>
   <si>
     <t xml:space="preserve">Rəhbərlik və hesabatlar əl ilə</t>
@@ -215,9 +209,6 @@
     <t xml:space="preserve">Aşağı</t>
   </si>
   <si>
-    <t xml:space="preserve">OBS-009, OBS-010</t>
-  </si>
-  <si>
     <t xml:space="preserve">HTTPS avtomatik yoxlanılıb; kuki bayraqları icra olunmayıb</t>
   </si>
   <si>
@@ -242,16 +233,13 @@
     <t xml:space="preserve">Performans və SEO</t>
   </si>
   <si>
-    <t xml:space="preserve">BUG-017, OBS-011</t>
+    <t xml:space="preserve">BUG-017, 030</t>
   </si>
   <si>
     <t xml:space="preserve">Yüklənmə müddəti yoxlanmayıb</t>
   </si>
   <si>
     <t xml:space="preserve">Çat və widget-lər</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OBS-012 (rədd edildi)</t>
   </si>
   <si>
     <t xml:space="preserve">Çat pəncərəsində mesaj göndərmə (UI-CHT-003, 004) əl ilə yoxlanmalıdır</t>
@@ -799,7 +787,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>10</v>
@@ -807,27 +795,27 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>20</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>6</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>7</v>
@@ -839,7 +827,7 @@
         <v>2</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>10</v>
@@ -847,7 +835,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>7</v>
@@ -859,15 +847,15 @@
         <v>4</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>7</v>
@@ -879,7 +867,7 @@
         <v>3</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>10</v>
@@ -887,7 +875,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>7</v>
@@ -899,81 +887,81 @@
         <v>4</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="E12" s="3" t="s">
+      <c r="F12" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>8</v>
       </c>
       <c r="E13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>4</v>
@@ -982,118 +970,118 @@
         <v>10</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>10</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>6</v>
@@ -1107,102 +1095,102 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1238,15 +1226,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B2" s="5" t="n">
         <f aca="false">COUNTA('Əhatə statusu'!A2:A25)</f>
@@ -1264,7 +1252,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B4" s="5" t="n">
         <f aca="false">COUNTIF('Əhatə statusu'!B2:B25,"Əl ilə baxılıb")</f>
@@ -1273,7 +1261,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B5" s="5" t="n">
         <f aca="false">COUNTIF('Əhatə statusu'!B2:B25,"İcra olunmayıb")</f>
@@ -1291,7 +1279,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B7" s="6" t="n">
         <f aca="false">B3/B2</f>
@@ -1300,7 +1288,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B8" s="5" t="n">
         <f aca="false">COUNTIFS('Əhatə statusu'!B2:B25,"İcra olunmayıb",'Əhatə statusu'!C2:C25,"Yüksək")</f>

--- a/docs/Final_Project_UI_Ehate_Statusu.xlsx
+++ b/docs/Final_Project_UI_Ehate_Statusu.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="77">
   <si>
     <t xml:space="preserve">Modul</t>
   </si>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">Yüksək</t>
   </si>
   <si>
-    <t xml:space="preserve">BUG-008, 009, 010, 032</t>
+    <t xml:space="preserve">BUG-008, 009, 010</t>
   </si>
   <si>
     <t xml:space="preserve">-</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">Axtarış</t>
   </si>
   <si>
-    <t xml:space="preserve">BUG-015, 016, 027, 028</t>
+    <t xml:space="preserve">BUG-015, 016</t>
   </si>
   <si>
     <t xml:space="preserve">Responsiv və mobil</t>
@@ -125,9 +125,6 @@
     <t xml:space="preserve">Kartlar</t>
   </si>
   <si>
-    <t xml:space="preserve">BUG-029</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kart detalları və sıralama manual qalır</t>
   </si>
   <si>
@@ -171,9 +168,6 @@
   </si>
   <si>
     <t xml:space="preserve">Kampaniyalar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUG-031</t>
   </si>
   <si>
     <t xml:space="preserve">Detal səhifəsi yoxlanıldı; bitmiş kampaniya siyahıdadır</t>
@@ -907,15 +901,15 @@
         <v>4</v>
       </c>
       <c r="E11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>7</v>
@@ -927,15 +921,15 @@
         <v>7</v>
       </c>
       <c r="E12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>7</v>
@@ -947,15 +941,15 @@
         <v>8</v>
       </c>
       <c r="E13" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>7</v>
@@ -970,12 +964,12 @@
         <v>10</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>7</v>
@@ -990,12 +984,12 @@
         <v>10</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>7</v>
@@ -1007,15 +1001,15 @@
         <v>10</v>
       </c>
       <c r="E16" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>7</v>
@@ -1027,15 +1021,15 @@
         <v>2</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>7</v>
@@ -1047,15 +1041,15 @@
         <v>1</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>7</v>
@@ -1067,15 +1061,15 @@
         <v>1</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>7</v>
@@ -1095,13 +1089,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -1110,78 +1104,78 @@
         <v>10</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>0</v>
@@ -1190,7 +1184,7 @@
         <v>10</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1226,15 +1220,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B2" s="5" t="n">
         <f aca="false">COUNTA('Əhatə statusu'!A2:A25)</f>
@@ -1252,7 +1246,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B4" s="5" t="n">
         <f aca="false">COUNTIF('Əhatə statusu'!B2:B25,"Əl ilə baxılıb")</f>
@@ -1261,7 +1255,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B5" s="5" t="n">
         <f aca="false">COUNTIF('Əhatə statusu'!B2:B25,"İcra olunmayıb")</f>
@@ -1279,7 +1273,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B7" s="6" t="n">
         <f aca="false">B3/B2</f>
@@ -1288,7 +1282,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B8" s="5" t="n">
         <f aca="false">COUNTIFS('Əhatə statusu'!B2:B25,"İcra olunmayıb",'Əhatə statusu'!C2:C25,"Yüksək")</f>
